--- a/Docs/干员、卡牌设计/设定.xlsx
+++ b/Docs/干员、卡牌设计/设定.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\ArkWars\Debuggers\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\ArkWars\Docs\干员、卡牌设计\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F084D15E-9A6B-4656-8601-797F51C7481B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAE1ABEE-2EF3-4E36-8911-9298D53BF91E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="角色" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="490">
   <si>
     <t>名称</t>
     <phoneticPr fontId="7" type="noConversion"/>
@@ -501,14 +501,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>当你受到伤害后，你摸1张牌并将1张手牌置于干员牌上称为“我执”，随后你可以视为对伤害来源使用一张“我执”中的牌。你的手牌上限额外增加X（X为“我执”的数量），你的血量不大于“我执”时，你无法被指向类回复卡牌指定。</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>出牌阶段限一次，你获得任意张“我执”并使用，以此法造成伤害的卡牌令你回复1点血量，回合结束时，你失去X点血量。（X为获得“我执”的数量减去造成伤害数）</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>7/7</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -526,10 +518,6 @@
   </si>
   <si>
     <t>当你进入濒死状态时，你可以移除场上所有的“寒冷”标记令你与伤害来源获得“冻结”，然后减少2点血量上限并血量回复至X并摸X张牌。（X为移除的“寒冷”标记数量且至多为5。）</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>你每回合使用的前2张卡牌可以额外指定一个目标，回合结束时，你对所有拥有“冻结”的角色造成1点法术伤害并移除“冻结”。</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
@@ -1230,21 +1218,22 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>每当你使用或打出</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>2张手牌，令你的一张手牌获得：
-①：伤害+1。
-②：无次数限制。
-③：无法响应。</t>
+    <t>主动技</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>出牌阶段结束时，直到你的下回合结束，你无法使用伤害类卡牌并将攻击范围调整为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>3，当</t>
     </r>
     <r>
       <rPr>
@@ -1254,57 +1243,6 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">
-④：结算后视为再次使用。</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>出牌阶段限一次，你可以选择一名角色对其使用你的一张非装备牌（以此法使用的牌无距离、次数限制）并摸X张牌，随后其视为在你的攻击范围内，本回合内你无法使用同类型卡牌。（X为你的攻击范围）</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>当受到过你回复的角色血量发生变化时，你与其各摸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>1张牌。</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>主动技</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>出牌阶段结束时，直到你的下回合结束，你无法使用伤害类卡牌并将攻击范围调整为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>3，当</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
       <t>攻击范围内角色的准备阶段开始时，你可以弃置一张伤害类卡牌，若卡牌颜色为红，则令其回复1点血量，若卡牌颜色为黑，则令其下一次受到法术伤害+1。</t>
     </r>
     <phoneticPr fontId="7" type="noConversion"/>
@@ -1387,10 +1325,6 @@
   </si>
   <si>
     <t>薇薇安娜</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>雷缪安</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
@@ -1982,10 +1916,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>你造成血量回复时摸1张牌，若目标角色拥有负面标记则随机移除1个并摸1张牌。出牌阶段限一次，你展示一名其他角色的一张手牌并获得，若为红色，则令该角色回复1点血量且此技能视为未发动过，若为黑色，则你令其下次受到伤害后摸2张牌。</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>限定技</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -2047,46 +1977,6 @@
   </si>
   <si>
     <t>每回合限一次，当你使用或打出一张牌后，可以从牌堆底摸一张牌展示并交给场上任意一名角色，若展示牌与使用牌类型相同，此技能视为未发动过。</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>当前角色回合结束时，若你的血量与手牌数均未发生变动，则你可以摸X张牌并将X张牌以任意顺序放回牌堆底。（X为你的血量上限）</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>游戏开始时，你获得“屏障”。当场上有“屏障”触发时，你与其各摸1张牌并令其视为对攻击范围内至多</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>2名角色使用一张【杀·法术】。</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>出牌阶段限，你可以弃置X张手牌并选择一名角色，令其获得“屏障”，以此法获得的“屏障”失效后，其回复1点血量并获得“庇护”。（X为目标当前血量除以</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>2向下取整且至少为1）</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>出牌阶段，你令下一张指向性单一目标卡牌不计次数限制且额外选择至多两个目标，该卡牌造成伤害时令对应目标获得“晕眩”，在该卡牌结算后你流失X点体力。（X为该卡牌选择目标数减去造成伤害数）</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
@@ -2175,22 +2065,6 @@
   </si>
   <si>
     <r>
-      <t>每名角色的回合结束时，若场上角色均受到过伤害，则你指定任意名角色回复</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>1点血量，随后令一名角色立刻执行一个额外回合，该回合内每当有角色的血量发生变化时，你与该角色各摸1张牌。</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t>对除你以外任意一名角色使用。将“旧日残影”置入该角色的判定区内，其需弃置一张与判定结果相同花色的手牌，若没有弃置则对其造成</t>
     </r>
     <r>
@@ -2247,26 +2121,6 @@
   </si>
   <si>
     <r>
-      <t>游戏开始时，你获得“屏障”，当你失去屏障时，回复1点血量并摸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>2张牌。每回合结束时，若你本回合没有受到伤害，则你可以弃置2张手牌获得“屏障”。你的“屏障”拥有上限为3。</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>出牌阶段，你失去一个“屏障”并令下一张使用的卡牌指定攻击范围内的所有角色且不可响应，若该卡牌造成伤害，则令目标获得“眩晕”。</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t>当你造成伤害时，你令目标获得“寒冷”，当场上拥有“寒冷”的角色受到伤害时，你摸</t>
     </r>
     <r>
@@ -2394,38 +2248,6 @@
         <charset val="128"/>
       </rPr>
       <t>3张牌视为对攻击范围内等量名其他角色使用一张【杀·物理】，若此【杀】造成伤害且该角色血量为除你之外全场最高，则令其获得“束缚”。</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>当你造成伤害时，你摸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>1张牌并弃置1张牌令目标获得“寒冷”，你使其“冻结”并移除所有“寒冷”标记。</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>当你造成伤害时，你令目标获得“寒冷”，你使其“冻结”并移除所有“寒冷”标记。你对“冻结”角色造成的伤害+1且每回合首次指定其为目标的卡牌额外结算</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="思源黑体 CN Bold"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>2次。你无法获得“冻结”。</t>
     </r>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -2955,6 +2777,324 @@
       </rPr>
       <t xml:space="preserve"> (梅花)</t>
     </r>
+  </si>
+  <si>
+    <t>岁</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>每当你使用或打出</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>2张手牌，令你的一张手牌获得：
+①：数值+1。
+②：无次数及范围限制。
+③：无法响应。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+④：结算后视为再次使用。</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>每名角色限一次，你可以选择一名角色对其使用你的一张手牌（以此法使用的牌无距离、次数限制），随后你摸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>2张牌并令目标其视为在你的攻击范围内。</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>其他角色出牌阶段开始时，你可以失去至多X点血量，令其摸X张牌，以此法获得的卡牌不计入手牌上限，当前回合内其每造成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1点伤害，你回复1点血量并摸1张牌。（X为你的体力上限且至少为1）</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>当你造成伤害时，你摸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1张牌并弃置1张牌令目标获得“寒冷”。</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>当你造成伤害时，你令目标获得“寒冷”。你对“冻结”角色造成的伤害+1且每回合指定其为目标的卡牌额外结算</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>2次。你无法获得“冻结”。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>回合结束时，你对所有拥有“冻结”的角色造成1点法术伤害并移除“冻结”。</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>每回合限一次，当你使用单目标卡牌指定一名角色时，你可以与其拼点：若你赢，你获得其一张牌令此牌无法响应且此技能视为未发动过；若你没赢，你获得双方本次拼点的牌。</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>攻击范围</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>3，使用【杀】攻击被抵消后，你可以弃置2张牌强制命中。</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>岩崩锤</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>游戏开始时，你获得“屏障”并将“岩崩锤”置于你的武器栏</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>。当你弃牌时，若弃置牌数量不小于2且颜色相同，则你获得“屏障”。当前回合结束时，若你本回合没有受到伤害，则你可以摸X张牌并弃置任意张牌（X为你的装备区卡牌数）。你的“屏障”拥有上限为3，当你失去屏障时，回复1点血量并摸2张牌。出牌阶段，你可以弃置3张手牌获得“岩崩锤”（无论它在哪）。</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>沃土予身</t>
+  </si>
+  <si>
+    <t>出牌阶段限一次，你获得任意张“我执”并回复等量血量，以此法获得的卡牌无次数限制，回合结束时，你失去X点血量。（X为获得“我执”的数量减去造成伤害数）</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>当你受到伤害后，你摸1张牌并将1张手牌置于干员牌上称为“我执”，随后你可以视为对伤害来源使用一张“我执”中的牌。回合开始时，你可以对自己造成1点伤害并摸X张牌替换等量的“我执”（X为你的已损失血量）。你的手牌上限额外增加Y（Y为“我执”的数量），你的血量不大于“我执”时，你无法被指向类回复卡牌指定。</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>幽隙栖萤</t>
+  </si>
+  <si>
+    <t>浮光泡影</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>出牌阶段开始时，你摸X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>张牌并展示，随后选择展示牌中拥有的一种花色，弃置对应花色的全部手牌并令等量角色获得“屏障”，以此法获得的“屏障”失去后令目标回复1点血量获得“庇护”（X为场上受伤角色数且至少为1）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>若你通过此技能弃置过全部花色，则修改“幽隙栖萤”。</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>恶业苦果</t>
+  </si>
+  <si>
+    <t>地狱变相</t>
+  </si>
+  <si>
+    <t>创伤性癔症</t>
+  </si>
+  <si>
+    <t>镜花水月</t>
+  </si>
+  <si>
+    <t>传承终焉</t>
+  </si>
+  <si>
+    <t>博览者的狂语</t>
+  </si>
+  <si>
+    <t>横扫架势</t>
+  </si>
+  <si>
+    <t>坚守阵线</t>
+  </si>
+  <si>
+    <t>探寻</t>
+  </si>
+  <si>
+    <t>洞悉</t>
+  </si>
+  <si>
+    <t>牌堆底的前X张牌始终对你可见，当前角色回合结束时，若你的血量与手牌数均未发生变动，则你可以摸X张牌并将X张牌以任意顺序放回牌堆底。（X为你的血量上限）</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>先贤化身</t>
+  </si>
+  <si>
+    <t>仁慈</t>
+  </si>
+  <si>
+    <t>蕾缪安</t>
+  </si>
+  <si>
+    <t>许可与手续</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>强制追思</t>
+  </si>
+  <si>
+    <t>火力电台</t>
+  </si>
+  <si>
+    <t>开火成瘾症</t>
+  </si>
+  <si>
+    <t>铁弦</t>
+  </si>
+  <si>
+    <t>旧日重现</t>
+  </si>
+  <si>
+    <t>每轮限一次，当前回合结束时，若有“屏障”被触发过，则你可以令一名角色摸“浮光泡影”弃置过的花色各一张。
+修改：每轮限一次，当前回合结束时，若有“屏障”被触发过，则你可以令一名角色摸“浮光泡影”弃置过的花色各一张，若摸牌角色为当前回合结束的角色，则令其执行一个额外的出牌阶段。</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>氤氲</t>
+  </si>
+  <si>
+    <t>云霭荫佑</t>
+  </si>
+  <si>
+    <r>
+      <t>你造成血量回复时摸1张牌，若目标角色拥有负面标记则随机移除1个并摸1张牌。出牌阶段至多X次，你展示牌堆顶的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1张卡牌并令一名角色获得，若为红色，则其下次受到伤害后你为其回复1点血量，若为黑色，则其下次受到伤害后摸2张牌。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（X为你当前手牌中的类型数）</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>每名角色的回合结束时，若场上角色均受到过伤害，则你指定任意名角色回复</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Bold"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1点血量并将手牌补充至上限，随后令一名角色立刻执行一个额外回合，该回合内每当有角色的血量发生变化时，你与该角色各摸1张牌。</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>出牌阶段，你令下一张指向性单一目标卡牌不计次数限制且额外选择至多两个目标，该卡牌造成伤害时令对应目标获得“晕眩”，在该卡牌结算后你失去X点血量。（X为该卡牌选择目标数减去造成伤害数）</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>灵活应变</t>
+  </si>
+  <si>
+    <t>出牌阶段，你可以弃置1张手牌卡牌销毁“沙地兽”。该卡牌离开宝物栏时销毁。</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3190,7 +3330,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3269,9 +3409,6 @@
     <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3295,9 +3432,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3348,6 +3482,18 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3369,17 +3515,23 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3669,7 +3821,7 @@
     <col min="3" max="3" width="12" style="17" customWidth="1"/>
     <col min="4" max="4" width="18.5" style="6" customWidth="1"/>
     <col min="5" max="5" width="16.5" style="14" customWidth="1"/>
-    <col min="6" max="6" width="117.375" style="13" customWidth="1"/>
+    <col min="6" max="6" width="119.625" style="13" customWidth="1"/>
     <col min="7" max="7" width="20.125" style="6" customWidth="1"/>
     <col min="8" max="8" width="16.5" style="8" customWidth="1"/>
     <col min="9" max="9" width="138.375" style="9" customWidth="1"/>
@@ -3689,57 +3841,57 @@
     <col min="28" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="33" customFormat="1" ht="91.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:18" s="32" customFormat="1" ht="91.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="32" t="s">
+        <v>272</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>224</v>
+      </c>
+      <c r="C1" s="32" t="s">
+        <v>273</v>
+      </c>
+      <c r="D1" s="32" t="s">
+        <v>274</v>
+      </c>
+      <c r="E1" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="F1" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="G1" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="H1" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="I1" s="32" t="s">
+        <v>278</v>
+      </c>
+      <c r="J1" s="32" t="s">
         <v>279</v>
       </c>
-      <c r="B1" s="33" t="s">
-        <v>230</v>
-      </c>
-      <c r="C1" s="33" t="s">
+      <c r="K1" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="L1" s="32" t="s">
         <v>280</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="M1" s="32" t="s">
         <v>281</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="N1" s="32" t="s">
         <v>282</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="O1" s="32" t="s">
         <v>283</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="P1" s="32" t="s">
         <v>284</v>
       </c>
-      <c r="H1" s="33" t="s">
-        <v>282</v>
-      </c>
-      <c r="I1" s="33" t="s">
+      <c r="R1" s="32" t="s">
         <v>285</v>
-      </c>
-      <c r="J1" s="33" t="s">
-        <v>286</v>
-      </c>
-      <c r="K1" s="33" t="s">
-        <v>282</v>
-      </c>
-      <c r="L1" s="33" t="s">
-        <v>287</v>
-      </c>
-      <c r="M1" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="N1" s="33" t="s">
-        <v>289</v>
-      </c>
-      <c r="O1" s="33" t="s">
-        <v>290</v>
-      </c>
-      <c r="P1" s="33" t="s">
-        <v>291</v>
-      </c>
-      <c r="R1" s="33" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="91.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -3747,24 +3899,28 @@
         <v>16</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C2" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="26"/>
+      <c r="D2" s="26" t="s">
+        <v>460</v>
+      </c>
       <c r="E2" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="F2" s="50" t="s">
-        <v>359</v>
-      </c>
-      <c r="G2" s="26"/>
+        <v>75</v>
+      </c>
+      <c r="F2" s="64" t="s">
+        <v>461</v>
+      </c>
+      <c r="G2" s="33" t="s">
+        <v>459</v>
+      </c>
       <c r="H2" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="I2" s="50" t="s">
-        <v>360</v>
+        <v>75</v>
+      </c>
+      <c r="I2" s="65" t="s">
+        <v>482</v>
       </c>
       <c r="J2" s="26"/>
       <c r="K2" s="19"/>
@@ -3780,24 +3936,28 @@
         <v>16</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C3" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="26"/>
+      <c r="D3" s="26" t="s">
+        <v>462</v>
+      </c>
       <c r="E3" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="F3" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="G3" s="26"/>
+      <c r="F3" s="64" t="s">
+        <v>458</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>463</v>
+      </c>
       <c r="H3" s="16" t="s">
         <v>100</v>
       </c>
       <c r="I3" s="18" t="s">
-        <v>111</v>
+        <v>457</v>
       </c>
       <c r="J3" s="26"/>
       <c r="K3" s="16"/>
@@ -3813,24 +3973,28 @@
         <v>16</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="D4" s="26"/>
+        <v>110</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>464</v>
+      </c>
       <c r="E4" s="16" t="s">
         <v>103</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="G4" s="26"/>
+        <v>111</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>465</v>
+      </c>
       <c r="H4" s="16" t="s">
         <v>100</v>
       </c>
       <c r="I4" s="18" t="s">
-        <v>361</v>
+        <v>487</v>
       </c>
       <c r="J4" s="26"/>
       <c r="K4" s="16"/>
@@ -3846,24 +4010,28 @@
         <v>12</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="D5" s="26"/>
+        <v>110</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>466</v>
+      </c>
       <c r="E5" s="16" t="s">
         <v>103</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="G5" s="26"/>
+      <c r="G5" s="26" t="s">
+        <v>467</v>
+      </c>
       <c r="H5" s="16" t="s">
         <v>99</v>
       </c>
       <c r="I5" s="18" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="J5" s="26"/>
       <c r="K5" s="16"/>
@@ -3879,17 +4047,19 @@
         <v>12</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="D6" s="26"/>
+      <c r="D6" s="26" t="s">
+        <v>468</v>
+      </c>
       <c r="E6" s="16" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F6" s="27" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G6" s="26"/>
       <c r="H6" s="16"/>
@@ -3908,24 +4078,28 @@
         <v>4</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="26"/>
+      <c r="D7" s="26" t="s">
+        <v>469</v>
+      </c>
       <c r="E7" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="F7" s="50" t="s">
-        <v>363</v>
-      </c>
-      <c r="G7" s="26"/>
+      <c r="F7" s="48" t="s">
+        <v>351</v>
+      </c>
+      <c r="G7" s="67" t="s">
+        <v>488</v>
+      </c>
       <c r="H7" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="I7" s="50" t="s">
-        <v>364</v>
+      <c r="I7" s="48" t="s">
+        <v>352</v>
       </c>
       <c r="J7" s="26"/>
       <c r="K7" s="16"/>
@@ -3947,24 +4121,28 @@
         <v>4</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="D8" s="26"/>
+        <v>122</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>470</v>
+      </c>
       <c r="E8" s="16" t="s">
         <v>99</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>357</v>
-      </c>
-      <c r="G8" s="26"/>
+        <v>349</v>
+      </c>
+      <c r="G8" s="26" t="s">
+        <v>471</v>
+      </c>
       <c r="H8" s="16" t="s">
         <v>99</v>
       </c>
       <c r="I8" s="18" t="s">
-        <v>358</v>
+        <v>472</v>
       </c>
       <c r="J8" s="26"/>
       <c r="K8" s="16"/>
@@ -3980,19 +4158,23 @@
         <v>9</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="D9" s="26"/>
+        <v>116</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>473</v>
+      </c>
       <c r="E9" s="16" t="s">
         <v>75</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>367</v>
-      </c>
-      <c r="G9" s="23"/>
+        <v>355</v>
+      </c>
+      <c r="G9" s="68" t="s">
+        <v>474</v>
+      </c>
       <c r="H9" s="19" t="s">
         <v>49</v>
       </c>
@@ -4013,10 +4195,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D10" s="26" t="s">
         <v>57</v>
@@ -4024,8 +4206,8 @@
       <c r="E10" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="F10" s="50" t="s">
-        <v>369</v>
+      <c r="F10" s="48" t="s">
+        <v>357</v>
       </c>
       <c r="G10" s="26" t="s">
         <v>56</v>
@@ -4051,43 +4233,43 @@
     </row>
     <row r="11" spans="1:18" ht="91.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="26" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="E11" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="F11" s="40" t="s">
-        <v>295</v>
+      <c r="F11" s="38" t="s">
+        <v>288</v>
       </c>
       <c r="G11" s="26" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="H11" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="I11" s="40" t="s">
-        <v>296</v>
+      <c r="I11" s="38" t="s">
+        <v>289</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="N11" s="7" t="s">
         <v>75</v>
       </c>
       <c r="O11" s="15" t="s">
-        <v>368</v>
-      </c>
-      <c r="P11" s="41" t="s">
-        <v>294</v>
+        <v>356</v>
+      </c>
+      <c r="P11" s="39" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="91.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -4095,24 +4277,28 @@
         <v>6</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>240</v>
+        <v>475</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="D12" s="26"/>
+        <v>122</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>476</v>
+      </c>
       <c r="E12" s="16" t="s">
         <v>50</v>
       </c>
       <c r="F12" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="G12" s="26"/>
+      <c r="G12" s="26" t="s">
+        <v>477</v>
+      </c>
       <c r="H12" s="16" t="s">
         <v>49</v>
       </c>
       <c r="I12" s="18" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="J12" s="26"/>
       <c r="K12" s="16"/>
@@ -4128,19 +4314,23 @@
         <v>6</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="D13" s="26"/>
+        <v>122</v>
+      </c>
+      <c r="D13" s="26" t="s">
+        <v>478</v>
+      </c>
       <c r="E13" s="16" t="s">
         <v>50</v>
       </c>
       <c r="F13" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="G13" s="26"/>
+      <c r="G13" s="26" t="s">
+        <v>479</v>
+      </c>
       <c r="H13" s="16" t="s">
         <v>49</v>
       </c>
@@ -4154,7 +4344,7 @@
         <v>54</v>
       </c>
       <c r="L13" s="18" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="M13" s="26"/>
       <c r="N13" s="16"/>
@@ -4167,24 +4357,28 @@
         <v>6</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="D14" s="26"/>
+        <v>123</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>480</v>
+      </c>
       <c r="E14" s="16" t="s">
         <v>75</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="G14" s="26"/>
+        <v>112</v>
+      </c>
+      <c r="G14" s="26" t="s">
+        <v>481</v>
+      </c>
       <c r="H14" s="16" t="s">
         <v>100</v>
       </c>
       <c r="I14" s="18" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="J14" s="26"/>
       <c r="K14" s="16"/>
@@ -4200,24 +4394,28 @@
         <v>10</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="D15" s="26"/>
+        <v>122</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>484</v>
+      </c>
       <c r="E15" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="18" t="s">
-        <v>347</v>
-      </c>
-      <c r="G15" s="26"/>
+      <c r="F15" s="64" t="s">
+        <v>485</v>
+      </c>
+      <c r="G15" s="26" t="s">
+        <v>483</v>
+      </c>
       <c r="H15" s="16" t="s">
-        <v>348</v>
-      </c>
-      <c r="I15" s="50" t="s">
-        <v>370</v>
+        <v>340</v>
+      </c>
+      <c r="I15" s="64" t="s">
+        <v>486</v>
       </c>
       <c r="J15" s="26"/>
       <c r="K15" s="16"/>
@@ -4228,29 +4426,28 @@
       <c r="P15" s="22"/>
       <c r="R15" s="11"/>
     </row>
-    <row r="16" spans="1:18" ht="91.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:18" ht="91.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A16" s="26" t="s">
         <v>10</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="D16" s="26"/>
+        <v>110</v>
+      </c>
       <c r="E16" s="16" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G16" s="26"/>
       <c r="H16" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="I16" s="50" t="s">
-        <v>129</v>
+        <v>117</v>
+      </c>
+      <c r="I16" s="48" t="s">
+        <v>126</v>
       </c>
       <c r="J16" s="26"/>
       <c r="K16" s="16"/>
@@ -4266,10 +4463,10 @@
         <v>5</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D17" s="26"/>
       <c r="E17" s="16" t="s">
@@ -4299,19 +4496,19 @@
         <v>5</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>108</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E18" s="16" t="s">
         <v>75</v>
       </c>
       <c r="F18" s="27" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G18" s="26"/>
       <c r="H18" s="16"/>
@@ -4320,22 +4517,22 @@
       <c r="K18" s="16"/>
       <c r="L18" s="18"/>
       <c r="M18" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="O18" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="P18" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="N18" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="O18" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="P18" s="26" t="s">
-        <v>136</v>
-      </c>
       <c r="Q18" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="R18" s="30" t="s">
-        <v>138</v>
+        <v>129</v>
+      </c>
+      <c r="R18" s="29" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="91.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -4343,24 +4540,24 @@
         <v>15</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="C19" s="17" t="s">
         <v>108</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="16" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="G19" s="26"/>
       <c r="H19" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="I19" s="50" t="s">
-        <v>141</v>
+        <v>137</v>
+      </c>
+      <c r="I19" s="48" t="s">
+        <v>138</v>
       </c>
       <c r="J19" s="26"/>
       <c r="K19" s="16"/>
@@ -4368,8 +4565,12 @@
       <c r="M19" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="N19" s="16"/>
-      <c r="O19" s="21"/>
+      <c r="N19" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="O19" s="21" t="s">
+        <v>489</v>
+      </c>
       <c r="P19" s="22"/>
       <c r="R19" s="11"/>
     </row>
@@ -4378,31 +4579,31 @@
         <v>15</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="C20" s="17" t="s">
         <v>109</v>
       </c>
       <c r="D20" s="26"/>
       <c r="E20" s="16" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F20" s="27" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G20" s="26"/>
       <c r="H20" s="16" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="I20" s="27" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="J20" s="26"/>
       <c r="K20" s="16"/>
       <c r="L20" s="18"/>
       <c r="M20" s="26"/>
       <c r="N20" s="16"/>
-      <c r="O20" s="29"/>
+      <c r="O20" s="28"/>
       <c r="P20" s="22"/>
       <c r="R20" s="11"/>
     </row>
@@ -4411,10 +4612,10 @@
         <v>2</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D21" s="26"/>
       <c r="E21" s="19" t="s">
@@ -4450,10 +4651,10 @@
         <v>2</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D22" s="26" t="s">
         <v>80</v>
@@ -4462,14 +4663,14 @@
         <v>78</v>
       </c>
       <c r="F22" s="27" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G22" s="26"/>
       <c r="H22" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="I22" s="31" t="s">
-        <v>224</v>
+      <c r="I22" s="30" t="s">
+        <v>218</v>
       </c>
       <c r="J22" s="26"/>
       <c r="K22" s="16"/>
@@ -4485,25 +4686,23 @@
         <v>2</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="D23" s="26"/>
+        <v>124</v>
+      </c>
+      <c r="D23" s="26" t="s">
+        <v>456</v>
+      </c>
       <c r="E23" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="F23" s="50" t="s">
-        <v>376</v>
+        <v>49</v>
+      </c>
+      <c r="F23" s="64" t="s">
+        <v>455</v>
       </c>
       <c r="G23" s="26"/>
-      <c r="H23" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="I23" s="18" t="s">
-        <v>377</v>
-      </c>
+      <c r="H23" s="16"/>
+      <c r="I23" s="18"/>
       <c r="J23" s="26"/>
       <c r="K23" s="16"/>
       <c r="L23" s="18"/>
@@ -4518,28 +4717,28 @@
         <v>2</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D24" s="26" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F24" s="27" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G24" s="26" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I24" s="27" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="J24" s="26"/>
       <c r="K24" s="16"/>
@@ -4555,26 +4754,26 @@
         <v>2</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="C25" s="17" t="s">
         <v>108</v>
       </c>
       <c r="D25" s="26"/>
       <c r="E25" s="16" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F25" s="27" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G25" s="26" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H25" s="16" t="s">
         <v>75</v>
       </c>
       <c r="I25" s="27" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="J25" s="26"/>
       <c r="K25" s="16"/>
@@ -4590,25 +4789,25 @@
         <v>2</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C26" s="17" t="s">
         <v>108</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="F26" s="40" t="s">
-        <v>299</v>
+        <v>217</v>
+      </c>
+      <c r="F26" s="38" t="s">
+        <v>292</v>
       </c>
       <c r="H26" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="I26" s="40" t="s">
-        <v>298</v>
+      <c r="I26" s="38" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:18" ht="91.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -4616,28 +4815,28 @@
         <v>46</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C27" s="17" t="s">
         <v>108</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F27" s="27" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G27" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="H27" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="I27" s="18" t="s">
         <v>149</v>
-      </c>
-      <c r="H27" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="I27" s="18" t="s">
-        <v>152</v>
       </c>
       <c r="J27" s="26"/>
       <c r="K27" s="16"/>
@@ -4653,24 +4852,24 @@
         <v>46</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F28" s="50" t="s">
-        <v>378</v>
-      </c>
-      <c r="G28" s="33"/>
+      <c r="F28" s="48" t="s">
+        <v>363</v>
+      </c>
+      <c r="G28" s="32"/>
       <c r="H28" s="16" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="I28" s="27" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="J28" s="26"/>
       <c r="K28" s="16"/>
@@ -4686,37 +4885,37 @@
         <v>1</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D29" s="26" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E29" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="F29" s="50" t="s">
-        <v>379</v>
+      <c r="F29" s="48" t="s">
+        <v>364</v>
       </c>
       <c r="G29" s="26" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="H29" s="16" t="s">
         <v>49</v>
       </c>
       <c r="I29" s="18" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="J29" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="L29" s="27" t="s">
         <v>169</v>
-      </c>
-      <c r="K29" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="L29" s="27" t="s">
-        <v>172</v>
       </c>
       <c r="M29" s="26" t="s">
         <v>28</v>
@@ -4725,7 +4924,7 @@
         <v>72</v>
       </c>
       <c r="O29" s="18" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="P29" s="22"/>
       <c r="R29" s="11"/>
@@ -4735,10 +4934,10 @@
         <v>1</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D30" s="26" t="s">
         <v>91</v>
@@ -4747,7 +4946,7 @@
         <v>75</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G30" s="26" t="s">
         <v>92</v>
@@ -4756,7 +4955,7 @@
         <v>75</v>
       </c>
       <c r="I30" s="18" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="J30" s="23"/>
       <c r="K30" s="16"/>
@@ -4772,17 +4971,17 @@
         <v>7</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D31" s="26"/>
       <c r="E31" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="F31" s="50" t="s">
-        <v>381</v>
+      <c r="F31" s="48" t="s">
+        <v>366</v>
       </c>
       <c r="G31" s="23"/>
       <c r="H31" s="16" t="s">
@@ -4801,7 +5000,7 @@
         <v>72</v>
       </c>
       <c r="O31" s="21" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="P31" s="22"/>
       <c r="R31" s="11"/>
@@ -4811,46 +5010,46 @@
         <v>7</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D32" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="F32" s="27" t="s">
+        <v>162</v>
+      </c>
+      <c r="G32" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="H32" s="34" t="s">
+        <v>137</v>
+      </c>
+      <c r="I32" s="48" t="s">
+        <v>367</v>
+      </c>
+      <c r="J32" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="K32" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="L32" s="27" t="s">
         <v>160</v>
-      </c>
-      <c r="E32" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="F32" s="27" t="s">
-        <v>165</v>
-      </c>
-      <c r="G32" s="34" t="s">
-        <v>161</v>
-      </c>
-      <c r="H32" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="I32" s="50" t="s">
-        <v>382</v>
-      </c>
-      <c r="J32" s="26" t="s">
-        <v>162</v>
-      </c>
-      <c r="K32" s="32" t="s">
-        <v>159</v>
-      </c>
-      <c r="L32" s="27" t="s">
-        <v>163</v>
       </c>
       <c r="M32" s="26" t="s">
         <v>22</v>
       </c>
       <c r="N32" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="O32" s="29" t="s">
-        <v>164</v>
+        <v>121</v>
+      </c>
+      <c r="O32" s="28" t="s">
+        <v>161</v>
       </c>
       <c r="P32" s="26" t="s">
         <v>23</v>
@@ -4858,8 +5057,8 @@
       <c r="Q32" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="R32" s="28" t="s">
-        <v>166</v>
+      <c r="R32" s="69" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="33" spans="1:18" ht="91.5" customHeight="1" x14ac:dyDescent="0.5">
@@ -4867,37 +5066,37 @@
         <v>7</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="D33" s="34" t="s">
-        <v>303</v>
+        <v>110</v>
+      </c>
+      <c r="D33" s="33" t="s">
+        <v>296</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>221</v>
-      </c>
-      <c r="F33" s="53" t="s">
-        <v>383</v>
-      </c>
-      <c r="G33" s="34" t="s">
-        <v>304</v>
-      </c>
-      <c r="H33" s="35" t="s">
+        <v>215</v>
+      </c>
+      <c r="F33" s="51" t="s">
+        <v>368</v>
+      </c>
+      <c r="G33" s="33" t="s">
+        <v>297</v>
+      </c>
+      <c r="H33" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="I33" s="40" t="s">
-        <v>301</v>
+      <c r="I33" s="38" t="s">
+        <v>294</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="N33" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="O33" s="42" t="s">
-        <v>302</v>
+      <c r="O33" s="40" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:18" ht="91.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -4905,26 +5104,26 @@
         <v>13</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D34" s="26" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="F34" s="50" t="s">
-        <v>410</v>
+        <v>212</v>
+      </c>
+      <c r="F34" s="48" t="s">
+        <v>393</v>
       </c>
       <c r="G34" s="26"/>
       <c r="H34" s="16" t="s">
-        <v>216</v>
-      </c>
-      <c r="I34" s="50" t="s">
-        <v>384</v>
+        <v>213</v>
+      </c>
+      <c r="I34" s="48" t="s">
+        <v>369</v>
       </c>
       <c r="J34" s="26"/>
       <c r="K34" s="16"/>
@@ -4940,24 +5139,24 @@
         <v>13</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="C35" s="17" t="s">
         <v>108</v>
       </c>
       <c r="D35" s="26"/>
       <c r="E35" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="F35" s="50" t="s">
-        <v>385</v>
+        <v>212</v>
+      </c>
+      <c r="F35" s="48" t="s">
+        <v>370</v>
       </c>
       <c r="G35" s="26"/>
       <c r="H35" s="16" t="s">
-        <v>216</v>
-      </c>
-      <c r="I35" s="50" t="s">
-        <v>386</v>
+        <v>213</v>
+      </c>
+      <c r="I35" s="48" t="s">
+        <v>371</v>
       </c>
       <c r="J35" s="26"/>
       <c r="K35" s="16"/>
@@ -4973,17 +5172,17 @@
         <v>13</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D36" s="26"/>
       <c r="E36" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="F36" s="50" t="s">
-        <v>409</v>
+        <v>211</v>
+      </c>
+      <c r="F36" s="48" t="s">
+        <v>392</v>
       </c>
       <c r="G36" s="26"/>
       <c r="H36" s="16"/>
@@ -5002,24 +5201,24 @@
         <v>17</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="C37" s="17" t="s">
         <v>108</v>
       </c>
       <c r="D37" s="26"/>
       <c r="E37" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="F37" s="37" t="s">
-        <v>218</v>
+        <v>211</v>
+      </c>
+      <c r="F37" s="64" t="s">
+        <v>447</v>
       </c>
       <c r="G37" s="26"/>
       <c r="H37" s="16" t="s">
-        <v>216</v>
-      </c>
-      <c r="I37" s="18" t="s">
-        <v>219</v>
+        <v>213</v>
+      </c>
+      <c r="I37" s="64" t="s">
+        <v>448</v>
       </c>
       <c r="J37" s="26"/>
       <c r="K37" s="16"/>
@@ -5035,24 +5234,24 @@
         <v>17</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C38" s="17" t="s">
         <v>108</v>
       </c>
       <c r="D38" s="26"/>
-      <c r="E38" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="F38" s="38" t="s">
-        <v>220</v>
+      <c r="E38" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="F38" s="65" t="s">
+        <v>449</v>
       </c>
       <c r="G38" s="26"/>
       <c r="H38" s="16" t="s">
-        <v>216</v>
-      </c>
-      <c r="I38" s="50" t="s">
-        <v>408</v>
+        <v>213</v>
+      </c>
+      <c r="I38" s="64" t="s">
+        <v>391</v>
       </c>
       <c r="J38" s="26"/>
       <c r="K38" s="16"/>
@@ -5068,17 +5267,17 @@
         <v>8</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D39" s="26"/>
       <c r="E39" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F39" s="50" t="s">
-        <v>387</v>
+      <c r="F39" s="64" t="s">
+        <v>450</v>
       </c>
       <c r="G39" s="26"/>
       <c r="H39" s="16" t="s">
@@ -5092,7 +5291,7 @@
         <v>54</v>
       </c>
       <c r="L39" s="18" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M39" s="26"/>
       <c r="N39" s="16"/>
@@ -5105,24 +5304,24 @@
         <v>8</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D40" s="26"/>
       <c r="E40" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F40" s="50" t="s">
-        <v>388</v>
+      <c r="F40" s="64" t="s">
+        <v>451</v>
       </c>
       <c r="G40" s="26"/>
       <c r="H40" s="16" t="s">
         <v>75</v>
       </c>
       <c r="I40" s="18" t="s">
-        <v>117</v>
+        <v>452</v>
       </c>
       <c r="J40" s="26"/>
       <c r="K40" s="16"/>
@@ -5138,31 +5337,31 @@
         <v>8</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="F41" s="40" t="s">
-        <v>310</v>
+        <v>219</v>
+      </c>
+      <c r="F41" s="38" t="s">
+        <v>303</v>
       </c>
       <c r="H41" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="I41" s="53" t="s">
-        <v>389</v>
+      <c r="I41" s="51" t="s">
+        <v>372</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="N41" s="16" t="s">
         <v>71</v>
       </c>
       <c r="O41" s="15" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
     </row>
     <row r="42" spans="1:18" ht="91.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -5170,17 +5369,17 @@
         <v>11</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D42" s="26"/>
       <c r="E42" s="16" t="s">
         <v>50</v>
       </c>
       <c r="F42" s="18" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G42" s="26" t="s">
         <v>97</v>
@@ -5189,7 +5388,7 @@
         <v>75</v>
       </c>
       <c r="I42" s="18" t="s">
-        <v>390</v>
+        <v>373</v>
       </c>
       <c r="J42" s="26"/>
       <c r="K42" s="16"/>
@@ -5205,7 +5404,7 @@
         <v>11</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C43" s="17" t="s">
         <v>108</v>
@@ -5214,15 +5413,15 @@
       <c r="E43" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="F43" s="50" t="s">
-        <v>392</v>
+      <c r="F43" s="48" t="s">
+        <v>375</v>
       </c>
       <c r="G43" s="26"/>
       <c r="H43" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="I43" s="39" t="s">
-        <v>222</v>
+        <v>215</v>
+      </c>
+      <c r="I43" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="J43" s="26"/>
       <c r="K43" s="16"/>
@@ -5238,28 +5437,28 @@
         <v>11</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D44" s="26" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E44" s="16" t="s">
         <v>50</v>
       </c>
       <c r="F44" s="18" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="G44" s="26" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H44" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="I44" s="50" t="s">
-        <v>400</v>
+      <c r="I44" s="48" t="s">
+        <v>383</v>
       </c>
       <c r="J44" s="26"/>
       <c r="K44" s="16"/>
@@ -5275,24 +5474,24 @@
         <v>11</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="C45" s="17" t="s">
         <v>108</v>
       </c>
       <c r="D45" s="26"/>
       <c r="E45" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="F45" s="50" t="s">
-        <v>391</v>
+        <v>215</v>
+      </c>
+      <c r="F45" s="48" t="s">
+        <v>374</v>
       </c>
       <c r="G45" s="26"/>
       <c r="H45" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="I45" s="50" t="s">
-        <v>393</v>
+        <v>219</v>
+      </c>
+      <c r="I45" s="48" t="s">
+        <v>376</v>
       </c>
       <c r="J45" s="26"/>
       <c r="K45" s="16"/>
@@ -5308,24 +5507,24 @@
         <v>3</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D46" s="26"/>
       <c r="E46" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="F46" s="50" t="s">
-        <v>346</v>
+      <c r="F46" s="48" t="s">
+        <v>339</v>
       </c>
       <c r="G46" s="26"/>
       <c r="H46" s="16" t="s">
         <v>49</v>
       </c>
       <c r="I46" s="18" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
       <c r="J46" s="26"/>
       <c r="K46" s="16"/>
@@ -5338,80 +5537,80 @@
     </row>
     <row r="47" spans="1:18" ht="91.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A47" s="26" t="s">
-        <v>3</v>
+        <v>446</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="C47" s="17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D47" s="26" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="F47" s="39" t="s">
-        <v>314</v>
+        <v>219</v>
+      </c>
+      <c r="F47" s="37" t="s">
+        <v>307</v>
       </c>
       <c r="G47" s="26" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="H47" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="I47" s="50" t="s">
-        <v>396</v>
+        <v>215</v>
+      </c>
+      <c r="I47" s="48" t="s">
+        <v>379</v>
       </c>
       <c r="K47" s="16"/>
-      <c r="L47" s="39"/>
+      <c r="L47" s="37"/>
       <c r="M47" s="26" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="N47" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="O47" s="54" t="s">
-        <v>395</v>
+      <c r="O47" s="52" t="s">
+        <v>378</v>
       </c>
       <c r="P47" s="26" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="Q47" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="R47" s="51" t="s">
-        <v>397</v>
+      <c r="R47" s="49" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="48" spans="1:18" ht="91.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A48" s="26" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C48" s="17" t="s">
         <v>108</v>
       </c>
       <c r="D48" s="26" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="F48" s="53" t="s">
-        <v>407</v>
+        <v>219</v>
+      </c>
+      <c r="F48" s="51" t="s">
+        <v>390</v>
       </c>
       <c r="G48" s="26" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="H48" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="I48" s="53" t="s">
-        <v>398</v>
+      <c r="I48" s="51" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="49" spans="1:18" ht="91.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -5419,24 +5618,24 @@
         <v>14</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D49" s="26"/>
       <c r="E49" s="16" t="s">
-        <v>223</v>
-      </c>
-      <c r="F49" s="50" t="s">
-        <v>403</v>
+        <v>217</v>
+      </c>
+      <c r="F49" s="48" t="s">
+        <v>386</v>
       </c>
       <c r="G49" s="26"/>
       <c r="H49" s="16" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="I49" s="18" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="J49" s="26"/>
       <c r="K49" s="16"/>
@@ -5449,24 +5648,24 @@
         <v>14</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="C50" s="17" t="s">
         <v>108</v>
       </c>
       <c r="D50" s="26"/>
       <c r="E50" s="16" t="s">
-        <v>223</v>
-      </c>
-      <c r="F50" s="50" t="s">
-        <v>399</v>
+        <v>217</v>
+      </c>
+      <c r="F50" s="48" t="s">
+        <v>382</v>
       </c>
       <c r="G50" s="26"/>
       <c r="H50" s="16" t="s">
-        <v>322</v>
-      </c>
-      <c r="I50" s="50" t="s">
-        <v>402</v>
+        <v>315</v>
+      </c>
+      <c r="I50" s="48" t="s">
+        <v>385</v>
       </c>
       <c r="J50" s="26"/>
       <c r="K50" s="16"/>
@@ -5477,8 +5676,8 @@
       <c r="N50" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="O50" s="43" t="s">
-        <v>325</v>
+      <c r="O50" s="41" t="s">
+        <v>318</v>
       </c>
       <c r="P50" s="22"/>
       <c r="R50" s="11"/>
@@ -5488,26 +5687,26 @@
         <v>14</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="C51" s="17" t="s">
         <v>108</v>
       </c>
       <c r="D51" s="26" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="E51" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="F51" s="39" t="s">
-        <v>331</v>
+        <v>219</v>
+      </c>
+      <c r="F51" s="37" t="s">
+        <v>324</v>
       </c>
       <c r="G51" s="26"/>
       <c r="H51" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="I51" s="50" t="s">
-        <v>405</v>
+        <v>215</v>
+      </c>
+      <c r="I51" s="48" t="s">
+        <v>388</v>
       </c>
       <c r="J51" s="26"/>
       <c r="K51" s="16"/>
@@ -5523,24 +5722,24 @@
         <v>14</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="C52" s="17" t="s">
         <v>108</v>
       </c>
       <c r="D52" s="26"/>
       <c r="E52" s="16" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="F52" s="18" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="G52" s="26"/>
       <c r="H52" s="16" t="s">
-        <v>223</v>
-      </c>
-      <c r="I52" s="50" t="s">
-        <v>406</v>
+        <v>217</v>
+      </c>
+      <c r="I52" s="48" t="s">
+        <v>389</v>
       </c>
       <c r="J52" s="26"/>
       <c r="K52" s="16"/>
@@ -5568,12 +5767,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{446EB1FC-0FB5-4845-B71D-73D3B9D3439E}">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultColWidth="15.25" defaultRowHeight="63" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="20.625" style="11" customWidth="1"/>
-    <col min="3" max="3" width="96.75" style="44" customWidth="1"/>
+    <col min="3" max="3" width="96.75" style="42" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
@@ -5591,187 +5790,198 @@
       <c r="A2" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="43" t="s">
         <v>72</v>
       </c>
-      <c r="C2" s="44" t="s">
+      <c r="C2" s="42" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="26" t="s">
-        <v>330</v>
-      </c>
-      <c r="B3" s="45" t="s">
-        <v>328</v>
-      </c>
-      <c r="C3" s="42" t="s">
-        <v>329</v>
+        <v>323</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>321</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="C4" s="42" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="26" t="s">
-        <v>342</v>
-      </c>
-      <c r="B5" s="45" t="s">
+        <v>335</v>
+      </c>
+      <c r="B5" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="C5" s="52" t="s">
-        <v>352</v>
+      <c r="C5" s="50" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="26" t="s">
+        <v>336</v>
+      </c>
+      <c r="B6" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="50" t="s">
         <v>343</v>
-      </c>
-      <c r="B6" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="52" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="26" t="s">
-        <v>154</v>
-      </c>
-      <c r="B7" s="45" t="s">
+        <v>151</v>
+      </c>
+      <c r="B7" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="52" t="s">
-        <v>350</v>
+      <c r="C7" s="50" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="26" t="s">
-        <v>349</v>
-      </c>
-      <c r="B8" s="45" t="s">
+        <v>341</v>
+      </c>
+      <c r="B8" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="52" t="s">
-        <v>353</v>
+      <c r="C8" s="50" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="26" t="s">
-        <v>412</v>
-      </c>
-      <c r="B9" s="45" t="s">
+        <v>395</v>
+      </c>
+      <c r="B9" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="C9" s="52" t="s">
-        <v>411</v>
+      <c r="C9" s="50" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="26" t="s">
-        <v>146</v>
-      </c>
-      <c r="B10" s="45" t="s">
-        <v>147</v>
-      </c>
-      <c r="C10" s="52" t="s">
-        <v>373</v>
+        <v>143</v>
+      </c>
+      <c r="B10" s="43" t="s">
+        <v>144</v>
+      </c>
+      <c r="C10" s="50" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="26" t="s">
-        <v>344</v>
-      </c>
-      <c r="B11" s="45" t="s">
-        <v>147</v>
-      </c>
-      <c r="C11" s="52" t="s">
-        <v>326</v>
+        <v>337</v>
+      </c>
+      <c r="B11" s="43" t="s">
+        <v>144</v>
+      </c>
+      <c r="C11" s="50" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="26" t="s">
-        <v>366</v>
-      </c>
-      <c r="B12" s="45" t="s">
-        <v>147</v>
-      </c>
-      <c r="C12" s="52" t="s">
-        <v>365</v>
+        <v>354</v>
+      </c>
+      <c r="B12" s="43" t="s">
+        <v>144</v>
+      </c>
+      <c r="C12" s="50" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="C13" s="42" t="s">
+      <c r="C13" s="40" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="26" t="s">
-        <v>305</v>
-      </c>
-      <c r="B14" s="45" t="s">
+        <v>298</v>
+      </c>
+      <c r="B14" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="C14" s="42" t="s">
-        <v>306</v>
+      <c r="C14" s="40" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="B15" s="45" t="s">
-        <v>372</v>
-      </c>
-      <c r="C15" s="52" t="s">
-        <v>371</v>
+        <v>120</v>
+      </c>
+      <c r="B15" s="43" t="s">
+        <v>359</v>
+      </c>
+      <c r="C15" s="50" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="26" t="s">
-        <v>319</v>
-      </c>
-      <c r="B16" s="45" t="s">
-        <v>372</v>
-      </c>
-      <c r="C16" s="52" t="s">
-        <v>320</v>
+        <v>312</v>
+      </c>
+      <c r="B16" s="43" t="s">
+        <v>359</v>
+      </c>
+      <c r="C16" s="50" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="26" t="s">
-        <v>318</v>
-      </c>
-      <c r="B17" s="45" t="s">
-        <v>372</v>
-      </c>
-      <c r="C17" s="52" t="s">
-        <v>321</v>
+        <v>311</v>
+      </c>
+      <c r="B17" s="43" t="s">
+        <v>359</v>
+      </c>
+      <c r="C17" s="50" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="26" t="s">
-        <v>375</v>
-      </c>
-      <c r="B18" s="45" t="s">
-        <v>372</v>
-      </c>
-      <c r="C18" s="52" t="s">
-        <v>374</v>
+        <v>362</v>
+      </c>
+      <c r="B18" s="43" t="s">
+        <v>359</v>
+      </c>
+      <c r="C18" s="50" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="26" t="s">
+        <v>454</v>
+      </c>
+      <c r="B19" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="C19" s="66" t="s">
+        <v>453</v>
       </c>
     </row>
   </sheetData>
@@ -5790,659 +6000,654 @@
   <dimension ref="A1:E41"/>
   <sheetFormatPr defaultColWidth="13.5" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="13.5" style="65"/>
+    <col min="1" max="16384" width="13.5" style="55"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="53" t="s">
+        <v>396</v>
+      </c>
+      <c r="B1" s="53" t="s">
+        <v>443</v>
+      </c>
+      <c r="C1" s="53" t="s">
+        <v>397</v>
+      </c>
+      <c r="D1" s="53" t="s">
+        <v>444</v>
+      </c>
+      <c r="E1" s="53" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="56" t="s">
+        <v>398</v>
+      </c>
+      <c r="B2" s="54" t="s">
+        <v>399</v>
+      </c>
+      <c r="C2" s="54" t="s">
+        <v>402</v>
+      </c>
+      <c r="D2" s="54" t="s">
+        <v>402</v>
+      </c>
+      <c r="E2" s="54" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="56"/>
+      <c r="B3" s="54" t="s">
+        <v>400</v>
+      </c>
+      <c r="C3" s="54" t="s">
+        <v>403</v>
+      </c>
+      <c r="D3" s="54" t="s">
+        <v>403</v>
+      </c>
+      <c r="E3" s="54" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="56"/>
+      <c r="B4" s="54" t="s">
+        <v>401</v>
+      </c>
+      <c r="C4" s="54" t="s">
+        <v>404</v>
+      </c>
+      <c r="D4" s="54" t="s">
+        <v>405</v>
+      </c>
+      <c r="E4" s="54" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="56">
+        <v>2</v>
+      </c>
+      <c r="B5" s="54" t="s">
+        <v>408</v>
+      </c>
+      <c r="C5" s="54" t="s">
+        <v>408</v>
+      </c>
+      <c r="D5" s="54" t="s">
+        <v>411</v>
+      </c>
+      <c r="E5" s="54" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="56"/>
+      <c r="B6" s="54" t="s">
+        <v>408</v>
+      </c>
+      <c r="C6" s="54" t="s">
+        <v>408</v>
+      </c>
+      <c r="D6" s="54" t="s">
+        <v>412</v>
+      </c>
+      <c r="E6" s="54" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="56"/>
+      <c r="B7" s="54" t="s">
+        <v>409</v>
+      </c>
+      <c r="C7" s="54" t="s">
+        <v>410</v>
+      </c>
+      <c r="D7" s="54" t="s">
         <v>413</v>
       </c>
-      <c r="B1" s="62" t="s">
-        <v>460</v>
-      </c>
-      <c r="C1" s="62" t="s">
+      <c r="E7" s="54" t="s">
         <v>414</v>
       </c>
-      <c r="D1" s="62" t="s">
-        <v>461</v>
-      </c>
-      <c r="E1" s="62" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="63" t="s">
+    </row>
+    <row r="8" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="56">
+        <v>3</v>
+      </c>
+      <c r="B8" s="54" t="s">
+        <v>410</v>
+      </c>
+      <c r="C8" s="54" t="s">
+        <v>408</v>
+      </c>
+      <c r="D8" s="54" t="s">
+        <v>411</v>
+      </c>
+      <c r="E8" s="54" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="56"/>
+      <c r="B9" s="54" t="s">
         <v>415</v>
       </c>
-      <c r="B2" s="64" t="s">
+      <c r="C9" s="54" t="s">
         <v>416</v>
       </c>
-      <c r="C2" s="64" t="s">
+      <c r="D9" s="54" t="s">
+        <v>417</v>
+      </c>
+      <c r="E9" s="54" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="56"/>
+      <c r="B10" s="54" t="s">
+        <v>409</v>
+      </c>
+      <c r="C10" s="54" t="s">
+        <v>410</v>
+      </c>
+      <c r="D10" s="54" t="s">
+        <v>418</v>
+      </c>
+      <c r="E10" s="54" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="56">
+        <v>4</v>
+      </c>
+      <c r="B11" s="54" t="s">
+        <v>410</v>
+      </c>
+      <c r="C11" s="54" t="s">
+        <v>408</v>
+      </c>
+      <c r="D11" s="54" t="s">
+        <v>411</v>
+      </c>
+      <c r="E11" s="54" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="56"/>
+      <c r="B12" s="54" t="s">
+        <v>415</v>
+      </c>
+      <c r="C12" s="54" t="s">
+        <v>416</v>
+      </c>
+      <c r="D12" s="54" t="s">
+        <v>417</v>
+      </c>
+      <c r="E12" s="54" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="56"/>
+      <c r="B13" s="54" t="s">
         <v>419</v>
       </c>
-      <c r="D2" s="64" t="s">
+      <c r="C13" s="54" t="s">
         <v>419</v>
       </c>
-      <c r="E2" s="64" t="s">
+      <c r="D13" s="54" t="s">
+        <v>420</v>
+      </c>
+      <c r="E13" s="54" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="56">
+        <v>5</v>
+      </c>
+      <c r="B14" s="54" t="s">
+        <v>422</v>
+      </c>
+      <c r="C14" s="54" t="s">
+        <v>408</v>
+      </c>
+      <c r="D14" s="54" t="s">
+        <v>425</v>
+      </c>
+      <c r="E14" s="54" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="56"/>
+      <c r="B15" s="54" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="63"/>
-      <c r="B3" s="64" t="s">
+      <c r="C15" s="54" t="s">
+        <v>424</v>
+      </c>
+      <c r="D15" s="54" t="s">
+        <v>411</v>
+      </c>
+      <c r="E15" s="54" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="56"/>
+      <c r="B16" s="54" t="s">
+        <v>410</v>
+      </c>
+      <c r="C16" s="54" t="s">
+        <v>419</v>
+      </c>
+      <c r="D16" s="54" t="s">
+        <v>421</v>
+      </c>
+      <c r="E16" s="54" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="56">
+        <v>6</v>
+      </c>
+      <c r="B17" s="54" t="s">
+        <v>410</v>
+      </c>
+      <c r="C17" s="54" t="s">
+        <v>411</v>
+      </c>
+      <c r="D17" s="54" t="s">
+        <v>411</v>
+      </c>
+      <c r="E17" s="54" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="56"/>
+      <c r="B18" s="54" t="s">
+        <v>428</v>
+      </c>
+      <c r="C18" s="54" t="s">
+        <v>408</v>
+      </c>
+      <c r="D18" s="54" t="s">
+        <v>428</v>
+      </c>
+      <c r="E18" s="54" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="56"/>
+      <c r="B19" s="54" t="s">
+        <v>410</v>
+      </c>
+      <c r="C19" s="54" t="s">
+        <v>408</v>
+      </c>
+      <c r="D19" s="54" t="s">
+        <v>421</v>
+      </c>
+      <c r="E19" s="54" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="56">
+        <v>7</v>
+      </c>
+      <c r="B20" s="54" t="s">
+        <v>410</v>
+      </c>
+      <c r="C20" s="54" t="s">
+        <v>411</v>
+      </c>
+      <c r="D20" s="54" t="s">
+        <v>411</v>
+      </c>
+      <c r="E20" s="54" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="56"/>
+      <c r="B21" s="54" t="s">
+        <v>430</v>
+      </c>
+      <c r="C21" s="54" t="s">
+        <v>408</v>
+      </c>
+      <c r="D21" s="54" t="s">
+        <v>431</v>
+      </c>
+      <c r="E21" s="54" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="56"/>
+      <c r="B22" s="54" t="s">
+        <v>419</v>
+      </c>
+      <c r="C22" s="54" t="s">
+        <v>408</v>
+      </c>
+      <c r="D22" s="54" t="s">
+        <v>421</v>
+      </c>
+      <c r="E22" s="54" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="56">
+        <v>8</v>
+      </c>
+      <c r="B23" s="54" t="s">
+        <v>410</v>
+      </c>
+      <c r="C23" s="54" t="s">
+        <v>411</v>
+      </c>
+      <c r="D23" s="54" t="s">
+        <v>411</v>
+      </c>
+      <c r="E23" s="54" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="56"/>
+      <c r="B24" s="54" t="s">
+        <v>430</v>
+      </c>
+      <c r="C24" s="54" t="s">
+        <v>408</v>
+      </c>
+      <c r="D24" s="54" t="s">
+        <v>411</v>
+      </c>
+      <c r="E24" s="54" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="56"/>
+      <c r="B25" s="54" t="s">
+        <v>408</v>
+      </c>
+      <c r="C25" s="54" t="s">
+        <v>408</v>
+      </c>
+      <c r="D25" s="54" t="s">
+        <v>421</v>
+      </c>
+      <c r="E25" s="54" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="56">
+        <v>9</v>
+      </c>
+      <c r="B26" s="54" t="s">
+        <v>410</v>
+      </c>
+      <c r="C26" s="54" t="s">
+        <v>411</v>
+      </c>
+      <c r="D26" s="54" t="s">
+        <v>411</v>
+      </c>
+      <c r="E26" s="54" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="56"/>
+      <c r="B27" s="54" t="s">
+        <v>430</v>
+      </c>
+      <c r="C27" s="54" t="s">
+        <v>408</v>
+      </c>
+      <c r="D27" s="54" t="s">
+        <v>411</v>
+      </c>
+      <c r="E27" s="54" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="56"/>
+      <c r="B28" s="54" t="s">
+        <v>408</v>
+      </c>
+      <c r="C28" s="54" t="s">
+        <v>418</v>
+      </c>
+      <c r="D28" s="54" t="s">
+        <v>418</v>
+      </c>
+      <c r="E28" s="54" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="56">
+        <v>10</v>
+      </c>
+      <c r="B29" s="54" t="s">
+        <v>411</v>
+      </c>
+      <c r="C29" s="54" t="s">
+        <v>411</v>
+      </c>
+      <c r="D29" s="54" t="s">
+        <v>411</v>
+      </c>
+      <c r="E29" s="54" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="56"/>
+      <c r="B30" s="54" t="s">
+        <v>411</v>
+      </c>
+      <c r="C30" s="54" t="s">
+        <v>411</v>
+      </c>
+      <c r="D30" s="54" t="s">
+        <v>411</v>
+      </c>
+      <c r="E30" s="54" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="56"/>
+      <c r="B31" s="54" t="s">
+        <v>419</v>
+      </c>
+      <c r="C31" s="54" t="s">
+        <v>408</v>
+      </c>
+      <c r="D31" s="54" t="s">
+        <v>432</v>
+      </c>
+      <c r="E31" s="54" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="56" t="s">
+        <v>433</v>
+      </c>
+      <c r="B32" s="54" t="s">
+        <v>411</v>
+      </c>
+      <c r="C32" s="54" t="s">
+        <v>408</v>
+      </c>
+      <c r="D32" s="54" t="s">
+        <v>411</v>
+      </c>
+      <c r="E32" s="54" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="56"/>
+      <c r="B33" s="54" t="s">
+        <v>430</v>
+      </c>
+      <c r="C33" s="54" t="s">
+        <v>408</v>
+      </c>
+      <c r="D33" s="54" t="s">
+        <v>411</v>
+      </c>
+      <c r="E33" s="54" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="56"/>
+      <c r="B34" s="54" t="s">
+        <v>408</v>
+      </c>
+      <c r="C34" s="54" t="s">
+        <v>408</v>
+      </c>
+      <c r="D34" s="54" t="s">
+        <v>432</v>
+      </c>
+      <c r="E34" s="54" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="56" t="s">
+        <v>434</v>
+      </c>
+      <c r="B35" s="54" t="s">
+        <v>410</v>
+      </c>
+      <c r="C35" s="54" t="s">
+        <v>410</v>
+      </c>
+      <c r="D35" s="54" t="s">
+        <v>436</v>
+      </c>
+      <c r="E35" s="54" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="56"/>
+      <c r="B36" s="54" t="s">
         <v>417</v>
       </c>
-      <c r="C3" s="64" t="s">
-        <v>420</v>
-      </c>
-      <c r="D3" s="64" t="s">
-        <v>420</v>
-      </c>
-      <c r="E3" s="64" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="63"/>
-      <c r="B4" s="64" t="s">
-        <v>418</v>
-      </c>
-      <c r="C4" s="64" t="s">
-        <v>421</v>
-      </c>
-      <c r="D4" s="64" t="s">
-        <v>422</v>
-      </c>
-      <c r="E4" s="64" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="63">
-        <v>2</v>
-      </c>
-      <c r="B5" s="64" t="s">
-        <v>425</v>
-      </c>
-      <c r="C5" s="64" t="s">
-        <v>425</v>
-      </c>
-      <c r="D5" s="64" t="s">
-        <v>428</v>
-      </c>
-      <c r="E5" s="64" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="63"/>
-      <c r="B6" s="64" t="s">
-        <v>425</v>
-      </c>
-      <c r="C6" s="64" t="s">
-        <v>425</v>
-      </c>
-      <c r="D6" s="64" t="s">
-        <v>429</v>
-      </c>
-      <c r="E6" s="64" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="63"/>
-      <c r="B7" s="64" t="s">
-        <v>426</v>
-      </c>
-      <c r="C7" s="64" t="s">
-        <v>427</v>
-      </c>
-      <c r="D7" s="64" t="s">
-        <v>430</v>
-      </c>
-      <c r="E7" s="64" t="s">
+      <c r="C36" s="54" t="s">
+        <v>435</v>
+      </c>
+      <c r="D36" s="54" t="s">
+        <v>401</v>
+      </c>
+      <c r="E36" s="54" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="56"/>
+      <c r="B37" s="54" t="s">
+        <v>408</v>
+      </c>
+      <c r="C37" s="54" t="s">
+        <v>409</v>
+      </c>
+      <c r="D37" s="54" t="s">
+        <v>432</v>
+      </c>
+      <c r="E37" s="54" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="56"/>
+      <c r="B38" s="54" t="s">
+        <v>406</v>
+      </c>
+      <c r="C38" s="54" t="s">
+        <v>401</v>
+      </c>
+      <c r="D38" s="54" t="s">
+        <v>432</v>
+      </c>
+      <c r="E38" s="54" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="56" t="s">
+        <v>438</v>
+      </c>
+      <c r="B39" s="54" t="s">
+        <v>408</v>
+      </c>
+      <c r="C39" s="54" t="s">
+        <v>411</v>
+      </c>
+      <c r="D39" s="54" t="s">
+        <v>436</v>
+      </c>
+      <c r="E39" s="54" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="63">
-        <v>3</v>
-      </c>
-      <c r="B8" s="64" t="s">
-        <v>427</v>
-      </c>
-      <c r="C8" s="64" t="s">
-        <v>425</v>
-      </c>
-      <c r="D8" s="64" t="s">
-        <v>428</v>
-      </c>
-      <c r="E8" s="64" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="63"/>
-      <c r="B9" s="64" t="s">
+    <row r="40" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="56"/>
+      <c r="B40" s="54" t="s">
+        <v>439</v>
+      </c>
+      <c r="C40" s="54" t="s">
+        <v>440</v>
+      </c>
+      <c r="D40" s="54" t="s">
+        <v>401</v>
+      </c>
+      <c r="E40" s="54" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="56"/>
+      <c r="B41" s="54" t="s">
+        <v>401</v>
+      </c>
+      <c r="C41" s="54" t="s">
+        <v>441</v>
+      </c>
+      <c r="D41" s="54" t="s">
         <v>432</v>
       </c>
-      <c r="C9" s="64" t="s">
-        <v>433</v>
-      </c>
-      <c r="D9" s="64" t="s">
-        <v>434</v>
-      </c>
-      <c r="E9" s="64" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="63"/>
-      <c r="B10" s="64" t="s">
-        <v>426</v>
-      </c>
-      <c r="C10" s="64" t="s">
-        <v>427</v>
-      </c>
-      <c r="D10" s="64" t="s">
-        <v>435</v>
-      </c>
-      <c r="E10" s="64" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="63">
-        <v>4</v>
-      </c>
-      <c r="B11" s="64" t="s">
-        <v>427</v>
-      </c>
-      <c r="C11" s="64" t="s">
-        <v>425</v>
-      </c>
-      <c r="D11" s="64" t="s">
-        <v>428</v>
-      </c>
-      <c r="E11" s="64" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="63"/>
-      <c r="B12" s="64" t="s">
-        <v>432</v>
-      </c>
-      <c r="C12" s="64" t="s">
-        <v>433</v>
-      </c>
-      <c r="D12" s="64" t="s">
-        <v>434</v>
-      </c>
-      <c r="E12" s="64" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="63"/>
-      <c r="B13" s="64" t="s">
-        <v>436</v>
-      </c>
-      <c r="C13" s="64" t="s">
-        <v>436</v>
-      </c>
-      <c r="D13" s="64" t="s">
-        <v>437</v>
-      </c>
-      <c r="E13" s="64" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="63">
-        <v>5</v>
-      </c>
-      <c r="B14" s="64" t="s">
-        <v>439</v>
-      </c>
-      <c r="C14" s="64" t="s">
-        <v>425</v>
-      </c>
-      <c r="D14" s="64" t="s">
-        <v>442</v>
-      </c>
-      <c r="E14" s="64" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="63"/>
-      <c r="B15" s="64" t="s">
-        <v>440</v>
-      </c>
-      <c r="C15" s="64" t="s">
-        <v>441</v>
-      </c>
-      <c r="D15" s="64" t="s">
-        <v>428</v>
-      </c>
-      <c r="E15" s="64" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="63"/>
-      <c r="B16" s="64" t="s">
-        <v>427</v>
-      </c>
-      <c r="C16" s="64" t="s">
-        <v>436</v>
-      </c>
-      <c r="D16" s="64" t="s">
-        <v>438</v>
-      </c>
-      <c r="E16" s="64" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="63">
-        <v>6</v>
-      </c>
-      <c r="B17" s="64" t="s">
-        <v>427</v>
-      </c>
-      <c r="C17" s="64" t="s">
-        <v>428</v>
-      </c>
-      <c r="D17" s="64" t="s">
-        <v>428</v>
-      </c>
-      <c r="E17" s="64" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="63"/>
-      <c r="B18" s="64" t="s">
-        <v>445</v>
-      </c>
-      <c r="C18" s="64" t="s">
-        <v>425</v>
-      </c>
-      <c r="D18" s="64" t="s">
-        <v>445</v>
-      </c>
-      <c r="E18" s="64" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="63"/>
-      <c r="B19" s="64" t="s">
-        <v>427</v>
-      </c>
-      <c r="C19" s="64" t="s">
-        <v>425</v>
-      </c>
-      <c r="D19" s="64" t="s">
-        <v>438</v>
-      </c>
-      <c r="E19" s="64" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="63">
-        <v>7</v>
-      </c>
-      <c r="B20" s="64" t="s">
-        <v>427</v>
-      </c>
-      <c r="C20" s="64" t="s">
-        <v>428</v>
-      </c>
-      <c r="D20" s="64" t="s">
-        <v>428</v>
-      </c>
-      <c r="E20" s="64" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="63"/>
-      <c r="B21" s="64" t="s">
-        <v>447</v>
-      </c>
-      <c r="C21" s="64" t="s">
-        <v>425</v>
-      </c>
-      <c r="D21" s="64" t="s">
-        <v>448</v>
-      </c>
-      <c r="E21" s="64" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="63"/>
-      <c r="B22" s="64" t="s">
-        <v>436</v>
-      </c>
-      <c r="C22" s="64" t="s">
-        <v>425</v>
-      </c>
-      <c r="D22" s="64" t="s">
-        <v>438</v>
-      </c>
-      <c r="E22" s="64" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="63">
-        <v>8</v>
-      </c>
-      <c r="B23" s="64" t="s">
-        <v>427</v>
-      </c>
-      <c r="C23" s="64" t="s">
-        <v>428</v>
-      </c>
-      <c r="D23" s="64" t="s">
-        <v>428</v>
-      </c>
-      <c r="E23" s="64" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="63"/>
-      <c r="B24" s="64" t="s">
-        <v>447</v>
-      </c>
-      <c r="C24" s="64" t="s">
-        <v>425</v>
-      </c>
-      <c r="D24" s="64" t="s">
-        <v>428</v>
-      </c>
-      <c r="E24" s="64" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="63"/>
-      <c r="B25" s="64" t="s">
-        <v>425</v>
-      </c>
-      <c r="C25" s="64" t="s">
-        <v>425</v>
-      </c>
-      <c r="D25" s="64" t="s">
-        <v>438</v>
-      </c>
-      <c r="E25" s="64" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="63">
-        <v>9</v>
-      </c>
-      <c r="B26" s="64" t="s">
-        <v>427</v>
-      </c>
-      <c r="C26" s="64" t="s">
-        <v>428</v>
-      </c>
-      <c r="D26" s="64" t="s">
-        <v>428</v>
-      </c>
-      <c r="E26" s="64" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="63"/>
-      <c r="B27" s="64" t="s">
-        <v>447</v>
-      </c>
-      <c r="C27" s="64" t="s">
-        <v>425</v>
-      </c>
-      <c r="D27" s="64" t="s">
-        <v>428</v>
-      </c>
-      <c r="E27" s="64" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="63"/>
-      <c r="B28" s="64" t="s">
-        <v>425</v>
-      </c>
-      <c r="C28" s="64" t="s">
-        <v>435</v>
-      </c>
-      <c r="D28" s="64" t="s">
-        <v>435</v>
-      </c>
-      <c r="E28" s="64" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="63">
-        <v>10</v>
-      </c>
-      <c r="B29" s="64" t="s">
-        <v>428</v>
-      </c>
-      <c r="C29" s="64" t="s">
-        <v>428</v>
-      </c>
-      <c r="D29" s="64" t="s">
-        <v>428</v>
-      </c>
-      <c r="E29" s="64" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="63"/>
-      <c r="B30" s="64" t="s">
-        <v>428</v>
-      </c>
-      <c r="C30" s="64" t="s">
-        <v>428</v>
-      </c>
-      <c r="D30" s="64" t="s">
-        <v>428</v>
-      </c>
-      <c r="E30" s="64" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="63"/>
-      <c r="B31" s="64" t="s">
-        <v>436</v>
-      </c>
-      <c r="C31" s="64" t="s">
-        <v>425</v>
-      </c>
-      <c r="D31" s="64" t="s">
-        <v>449</v>
-      </c>
-      <c r="E31" s="64" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="63" t="s">
-        <v>450</v>
-      </c>
-      <c r="B32" s="64" t="s">
-        <v>428</v>
-      </c>
-      <c r="C32" s="64" t="s">
-        <v>425</v>
-      </c>
-      <c r="D32" s="64" t="s">
-        <v>428</v>
-      </c>
-      <c r="E32" s="64" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="63"/>
-      <c r="B33" s="64" t="s">
-        <v>447</v>
-      </c>
-      <c r="C33" s="64" t="s">
-        <v>425</v>
-      </c>
-      <c r="D33" s="64" t="s">
-        <v>428</v>
-      </c>
-      <c r="E33" s="64" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="63"/>
-      <c r="B34" s="64" t="s">
-        <v>425</v>
-      </c>
-      <c r="C34" s="64" t="s">
-        <v>425</v>
-      </c>
-      <c r="D34" s="64" t="s">
-        <v>449</v>
-      </c>
-      <c r="E34" s="64" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="63" t="s">
-        <v>451</v>
-      </c>
-      <c r="B35" s="64" t="s">
-        <v>427</v>
-      </c>
-      <c r="C35" s="64" t="s">
-        <v>427</v>
-      </c>
-      <c r="D35" s="64" t="s">
-        <v>453</v>
-      </c>
-      <c r="E35" s="64" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="63"/>
-      <c r="B36" s="64" t="s">
-        <v>434</v>
-      </c>
-      <c r="C36" s="64" t="s">
-        <v>452</v>
-      </c>
-      <c r="D36" s="64" t="s">
-        <v>418</v>
-      </c>
-      <c r="E36" s="64" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="63"/>
-      <c r="B37" s="64" t="s">
-        <v>425</v>
-      </c>
-      <c r="C37" s="64" t="s">
-        <v>426</v>
-      </c>
-      <c r="D37" s="64" t="s">
-        <v>449</v>
-      </c>
-      <c r="E37" s="64" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="63"/>
-      <c r="B38" s="64" t="s">
-        <v>423</v>
-      </c>
-      <c r="C38" s="64" t="s">
-        <v>418</v>
-      </c>
-      <c r="D38" s="64" t="s">
-        <v>449</v>
-      </c>
-      <c r="E38" s="64" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="63" t="s">
-        <v>455</v>
-      </c>
-      <c r="B39" s="64" t="s">
-        <v>425</v>
-      </c>
-      <c r="C39" s="64" t="s">
-        <v>428</v>
-      </c>
-      <c r="D39" s="64" t="s">
-        <v>453</v>
-      </c>
-      <c r="E39" s="64" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="63"/>
-      <c r="B40" s="64" t="s">
-        <v>456</v>
-      </c>
-      <c r="C40" s="64" t="s">
-        <v>457</v>
-      </c>
-      <c r="D40" s="64" t="s">
-        <v>418</v>
-      </c>
-      <c r="E40" s="64" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="63"/>
-      <c r="B41" s="64" t="s">
-        <v>418</v>
-      </c>
-      <c r="C41" s="64" t="s">
-        <v>458</v>
-      </c>
-      <c r="D41" s="64" t="s">
-        <v>449</v>
-      </c>
-      <c r="E41" s="64" t="s">
-        <v>418</v>
+      <c r="E41" s="54" t="s">
+        <v>401</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="A14:A16"/>
     <mergeCell ref="A17:A19"/>
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="A20:A22"/>
@@ -6451,6 +6656,11 @@
     <mergeCell ref="A29:A31"/>
     <mergeCell ref="A32:A34"/>
     <mergeCell ref="A35:A38"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A14:A16"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6464,265 +6674,265 @@
   <cols>
     <col min="1" max="1" width="19" style="26"/>
     <col min="2" max="2" width="19" style="16"/>
-    <col min="3" max="3" width="79.375" style="47" customWidth="1"/>
+    <col min="3" max="3" width="79.375" style="45" customWidth="1"/>
     <col min="4" max="16384" width="19" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="49" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" s="47" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="26" t="s">
-        <v>289</v>
-      </c>
-      <c r="B1" s="33" t="s">
+        <v>282</v>
+      </c>
+      <c r="B1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="33" t="s">
-        <v>335</v>
+      <c r="C1" s="32" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="55" t="s">
-        <v>336</v>
-      </c>
-      <c r="B2" s="45" t="s">
+      <c r="A2" s="57" t="s">
+        <v>329</v>
+      </c>
+      <c r="B2" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="38" t="s">
+      <c r="C2" s="36" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="55"/>
-      <c r="B3" s="45" t="s">
+      <c r="A3" s="57"/>
+      <c r="B3" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="38" t="s">
+      <c r="C3" s="36" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="46"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="38"/>
+      <c r="A4" s="44"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="36"/>
     </row>
     <row r="5" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="56" t="s">
-        <v>337</v>
-      </c>
-      <c r="B5" s="45" t="s">
+      <c r="A5" s="58" t="s">
+        <v>330</v>
+      </c>
+      <c r="B5" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="38" t="s">
+      <c r="C5" s="36" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="57"/>
-      <c r="B6" s="45" t="s">
+      <c r="A6" s="59"/>
+      <c r="B6" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="C6" s="36" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="57"/>
-      <c r="B7" s="45" t="s">
-        <v>338</v>
-      </c>
-      <c r="C7" s="48" t="s">
-        <v>339</v>
+      <c r="A7" s="59"/>
+      <c r="B7" s="43" t="s">
+        <v>331</v>
+      </c>
+      <c r="C7" s="46" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="58"/>
-      <c r="B8" s="45" t="s">
+      <c r="A8" s="60"/>
+      <c r="B8" s="43" t="s">
+        <v>173</v>
+      </c>
+      <c r="C8" s="36" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="43"/>
+      <c r="C9" s="36"/>
+    </row>
+    <row r="10" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="58" t="s">
+        <v>333</v>
+      </c>
+      <c r="B10" s="43" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="36" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="59"/>
+      <c r="B11" s="43" t="s">
+        <v>174</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="59"/>
+      <c r="B12" s="43" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="36" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="59"/>
+      <c r="B13" s="43" t="s">
+        <v>175</v>
+      </c>
+      <c r="C13" s="36" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="59"/>
+      <c r="B14" s="43" t="s">
         <v>176</v>
       </c>
-      <c r="C8" s="38" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="45"/>
-      <c r="C9" s="38"/>
-    </row>
-    <row r="10" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="56" t="s">
-        <v>340</v>
-      </c>
-      <c r="B10" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" s="38" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="57"/>
-      <c r="B11" s="45" t="s">
+      <c r="C14" s="36" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="59"/>
+      <c r="B15" s="43" t="s">
         <v>177</v>
       </c>
-      <c r="C11" s="38" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="57"/>
-      <c r="B12" s="45" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="38" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="57"/>
-      <c r="B13" s="45" t="s">
+      <c r="C15" s="36" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="59"/>
+      <c r="B16" s="43" t="s">
         <v>178</v>
       </c>
-      <c r="C13" s="38" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="57"/>
-      <c r="B14" s="45" t="s">
+      <c r="C16" s="36" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="59"/>
+      <c r="B17" s="43" t="s">
         <v>179</v>
       </c>
-      <c r="C14" s="38" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="57"/>
-      <c r="B15" s="45" t="s">
+      <c r="C17" s="36" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="59"/>
+      <c r="B18" s="43" t="s">
         <v>180</v>
       </c>
-      <c r="C15" s="38" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="57"/>
-      <c r="B16" s="45" t="s">
+      <c r="C18" s="36" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="59"/>
+      <c r="B19" s="43" t="s">
         <v>181</v>
       </c>
-      <c r="C16" s="38" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="57"/>
-      <c r="B17" s="45" t="s">
+      <c r="C19" s="36" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="59"/>
+      <c r="B20" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="36" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="59"/>
+      <c r="B21" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="36" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="60"/>
+      <c r="B22" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22" s="36" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="58" t="s">
+        <v>334</v>
+      </c>
+      <c r="B24" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="36" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="59"/>
+      <c r="B25" s="43" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="36" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="59"/>
+      <c r="B26" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="36" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="59"/>
+      <c r="B27" s="43" t="s">
         <v>182</v>
       </c>
-      <c r="C17" s="38" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="57"/>
-      <c r="B18" s="45" t="s">
+      <c r="C27" s="36" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="60"/>
+      <c r="B28" s="43" t="s">
         <v>183</v>
       </c>
-      <c r="C18" s="38" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="57"/>
-      <c r="B19" s="45" t="s">
-        <v>184</v>
-      </c>
-      <c r="C19" s="38" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="57"/>
-      <c r="B20" s="45" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20" s="38" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="57"/>
-      <c r="B21" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="C21" s="38" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="58"/>
-      <c r="B22" s="45" t="s">
-        <v>104</v>
-      </c>
-      <c r="C22" s="38" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="56" t="s">
-        <v>341</v>
-      </c>
-      <c r="B24" s="45" t="s">
-        <v>59</v>
-      </c>
-      <c r="C24" s="38" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="57"/>
-      <c r="B25" s="45" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" s="38" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="57"/>
-      <c r="B26" s="45" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" s="38" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="57"/>
-      <c r="B27" s="45" t="s">
-        <v>185</v>
-      </c>
-      <c r="C27" s="38" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="58"/>
-      <c r="B28" s="45" t="s">
-        <v>186</v>
-      </c>
-      <c r="C28" s="38" t="s">
+      <c r="C28" s="36" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="45"/>
-      <c r="C30" s="38"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="36"/>
     </row>
     <row r="31" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="45"/>
-      <c r="C31" s="38"/>
+      <c r="B31" s="43"/>
+      <c r="C31" s="36"/>
     </row>
     <row r="32" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="45"/>
-      <c r="C32" s="38"/>
+      <c r="B32" s="43"/>
+      <c r="C32" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -6751,164 +6961,164 @@
   <sheetData>
     <row r="1" spans="1:6" s="2" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="56" t="s">
+      <c r="A2" s="58" t="s">
+        <v>187</v>
+      </c>
+      <c r="B2" s="35" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2" s="61" t="s">
+        <v>326</v>
+      </c>
+      <c r="D2" s="58" t="s">
+        <v>338</v>
+      </c>
+      <c r="E2" s="35" t="s">
+        <v>196</v>
+      </c>
+      <c r="F2" s="35" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="59"/>
+      <c r="B3" s="35" t="s">
+        <v>188</v>
+      </c>
+      <c r="C3" s="63"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="35" t="s">
+        <v>185</v>
+      </c>
+      <c r="F3" s="35" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="59"/>
+      <c r="B4" s="35" t="s">
+        <v>189</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="59"/>
+      <c r="E4" s="61" t="s">
+        <v>186</v>
+      </c>
+      <c r="F4" s="35" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="59"/>
+      <c r="B5" s="35" t="s">
         <v>190</v>
       </c>
-      <c r="B2" s="36" t="s">
+      <c r="C5" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="59"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="35" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="59"/>
+      <c r="B6" s="35" t="s">
         <v>191</v>
       </c>
-      <c r="C2" s="59" t="s">
-        <v>333</v>
-      </c>
-      <c r="D2" s="56" t="s">
-        <v>345</v>
-      </c>
-      <c r="E2" s="36" t="s">
+      <c r="C6" s="61" t="s">
+        <v>327</v>
+      </c>
+      <c r="D6" s="59"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="35" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="60"/>
+      <c r="B7" s="35" t="s">
+        <v>191</v>
+      </c>
+      <c r="C7" s="63"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="61" t="s">
+        <v>192</v>
+      </c>
+      <c r="F7" s="35" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D8" s="59"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="35" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D9" s="59"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="35" t="s">
         <v>199</v>
       </c>
-      <c r="F2" s="36" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="57"/>
-      <c r="B3" s="36" t="s">
-        <v>191</v>
-      </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="36" t="s">
-        <v>188</v>
-      </c>
-      <c r="F3" s="36" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="57"/>
-      <c r="B4" s="36" t="s">
-        <v>192</v>
-      </c>
-      <c r="C4" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="57"/>
-      <c r="E4" s="59" t="s">
-        <v>189</v>
-      </c>
-      <c r="F4" s="36" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="57"/>
-      <c r="B5" s="36" t="s">
+    </row>
+    <row r="10" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D10" s="59"/>
+      <c r="E10" s="61" t="s">
         <v>193</v>
       </c>
-      <c r="C5" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="57"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="36" t="s">
+      <c r="F10" s="35" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="57"/>
-      <c r="B6" s="36" t="s">
+    <row r="11" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D11" s="59"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="35" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D12" s="59"/>
+      <c r="E12" s="63"/>
+      <c r="F12" s="35" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D13" s="59"/>
+      <c r="E13" s="61" t="s">
         <v>194</v>
       </c>
-      <c r="C6" s="59" t="s">
-        <v>334</v>
-      </c>
-      <c r="D6" s="57"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="36" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="58"/>
-      <c r="B7" s="36" t="s">
-        <v>194</v>
-      </c>
-      <c r="C7" s="61"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="59" t="s">
+      <c r="F13" s="35" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D14" s="59"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="35" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D15" s="59"/>
+      <c r="E15" s="63"/>
+      <c r="F15" s="35" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D16" s="60"/>
+      <c r="E16" s="35" t="s">
         <v>195</v>
       </c>
-      <c r="F7" s="36" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D8" s="57"/>
-      <c r="E8" s="60"/>
-      <c r="F8" s="36" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D9" s="57"/>
-      <c r="E9" s="61"/>
-      <c r="F9" s="36" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D10" s="57"/>
-      <c r="E10" s="59" t="s">
-        <v>196</v>
-      </c>
-      <c r="F10" s="36" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D11" s="57"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="36" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D12" s="57"/>
-      <c r="E12" s="61"/>
-      <c r="F12" s="36" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D13" s="57"/>
-      <c r="E13" s="59" t="s">
-        <v>197</v>
-      </c>
-      <c r="F13" s="36" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D14" s="57"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="36" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D15" s="57"/>
-      <c r="E15" s="61"/>
-      <c r="F15" s="36" t="s">
+      <c r="F16" s="35" t="s">
         <v>201</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D16" s="58"/>
-      <c r="E16" s="36" t="s">
-        <v>198</v>
-      </c>
-      <c r="F16" s="36" t="s">
-        <v>204</v>
       </c>
     </row>
   </sheetData>
